--- a/data_extactor/batch_10_fa/trimmed/batch_0094_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0094_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | یادگیری فعال | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | تولید مواد غذایی | مدیریت و امور اداری | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>تولید و فرآوری | مکانیک | تولید مواد غذایی | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراک | ثبات دست و بازو | دقت در کنترل | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | سرعت ادراکی | ثبات دست و بازو | دقت کنترل | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان بچ‌سازی و فرمولاسیون مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت صنعتی غذا | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و دیگ‌های صنعتی | اپراتورهای کمپرسور گاز و ایستگاه‌های پمپاژ گاز | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی و تقطیر</t>
+          <t>تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مکانیک‌های ماشین‌آلات صنعتی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و خدمات فردی | مکانیک | طراحی</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | مکانیک | طراحی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | دقت در کنترل | توجه انتخابی | چابکی دستی | چابکی انگشتان | تجسم فضایی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | توجه انتخابی | مهارت دستی | مهارت انگشتان | تجسم</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>برشکاران دستی قطعات | کارگران پرداخت‌کاری و سنگ‌زنی دستی | طلاسازان و سازندگان مصنوعات قیمتی و فلزات گرانبها | نشانه‌گذاران و خط‌کشان خطوط برش قطعات فلزی و پلاستیکی | مدل‌سازان فلزی و پلاستیکی | تکنسین‌ها و کارگران مراحل پیش از چاپ | سنگ‌تراشان و حکاکان سنگ در خطوط تولید</t>
+          <t>برشکاران و پیرایشگران دستی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | مدل‌سازان فلز و پلاستیک | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | سنگ‌تراشان و حکاکان صنعتی سنگ</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت در کنترل | دید نزدیک | هماهنگی اندام‌ها | توجه انتخابی</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>برشکاران دستی قطعات | سازندگان و لمینیت‌کاران قطعات فایبرگلاس | قالب‌سازان و ماهیچه‌سازان ریخته‌گری چدن و فولاد | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | سفالگران خطوط تولید | سنگ‌تراشان و حکاکان سنگ در خطوط تولید</t>
+          <t>برشکاران و پیرایشگران دستی | لایه‌نشانان و سازندگان فایبرگلاس | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | سفالگران خطوط تولید و کارگاهی | سنگ‌تراشان و حکاکان صنعتی سنگ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Corel Paint Shop Pro | نرم‌افزار مدیریت موجودی | نرم‌افزار ثبت ساعت کار | Microsoft Excel | Microsoft Word</t>
+          <t>Corel Paint Shop Pro | نرم‌افزار مدیریت موجودی | نرم‌افزار ثبت ساعت کار | Microsoft Excel | نرم‌افزار ثبت زمان</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مدیریت و امور اداری | طراحی | آموزش و تدریس</t>
+          <t>ریاضیات | تولید و فرآوری | مکانیک | زبان انگلیسی | مدیریت و اداره | طراحی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | چابکی دستی | دقت در کنترل | چابکی انگشتان | قدرت بالاتنه | تجسم فضایی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت دستی | دقت کنترل | مهارت انگشتان | قدرت تنه | تجسم</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بنایان و آجرچین‌ها | حکاکان و اسیدکاران | کارگران پرداخت‌کاری و سنگ‌زنی دستی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | کارگران استخراج و شکافتن سنگ در معدن | سنگ‌چین‌ها و سنّت‌تراشان ساختمانی | کاشی‌کاران و سنگ‌کاران ساختمانی</t>
+          <t>بنایان و سفت‌کاران ساختمان | حکاکان و اسیدکاران | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | سنگ‌شکنان و برش‌کاران سنگ معدن | سنگ‌کاران ساختمانی | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار صدور فاکتور و صورت‌حساب | نرم‌افزار مدیریت موجودی | Microsoft Excel | Microsoft Outlook</t>
+          <t>نرم‌افزار صدور صورتحساب | نرم‌افزار مدیریت موجودی | Microsoft Excel | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | مکانیک | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | ریاضیات | زبان انگلیسی</t>
+          <t>تولید و فرآوری | طراحی | مکانیک | خدمات مشتری و شخصی | مهندسی و فناوری | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | دقت در کنترل | زمان واکنش | تجسم فضایی | چابکی دستی | چابکی انگشتان</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | دقت کنترل | زمان عکس‌العمل | تجسم | مهارت دستی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | کارگران پرداخت‌کاری و سنگ‌زنی دستی | تنظیم‌کنندگان و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | تکنسین‌های آزمایشگاه اپتیک و ساخت عدسی | سنگ‌تراشان و حکاکان سنگ در خطوط تولید</t>
+          <t>تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | سنگ‌تراشان و حکاکان صنعتی سنگ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>هنرهای تجسمی | تولید و فرآوری | طراحی | خدمات مشتریان و خدمات فردی | شیمی | مدیریت و امور اداری | فروش و بازاریابی</t>
+          <t>هنرهای زیبا | تولید و فرآوری | طراحی | خدمات مشتری و شخصی | شیمی | مدیریت و اداره | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دقت در کنترل | دید نزدیک | تجسم فضایی | اصالت و خلاقیت</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | تجسم | اصالت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>هنرمندان صنایع دستی | قالب‌سازان و ماهیچه‌سازان ریخته‌گری چدن و فولاد | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | کارگران پرداخت‌کاری و سنگ‌زنی دستی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | کارگران نقاشی صنعتی، پوشش‌دهی و تزیین | تعمیرکاران نسوزها و جداره‌های کوره</t>
+          <t>هنرمندان صنایع دستی | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت در کنترل | حساسیت به مسئله | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | توجه انتخابی</t>
+          <t>بینایی نزدیک | دقت کنترل | حساسیت به مسئله | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش و اسلایسر | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران صحافی و خدمات تکمیلی چاپ</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران صحافی و تکمیل چاپ</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری | مکانیک</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | ثبات دست و بازو | دقت در کنترل | هماهنگی اندام‌ها | قدرت بالاتنه | چابکی انگشتان | دید نزدیک</t>
+          <t>مهارت دستی | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | قدرت تنه | مهارت انگشتان | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>صافکاران و تعمیرکاران بدنه خودرو | مونتاژکاران موتور و ماشین‌آلات صنعتی | سازندگان و لمینیت‌کاران قطعات فایبرگلاس | مکانیک‌های ماشین‌آلات صنعتی | قالب‌ریزان و شکل‌دهندگان مواد غیرفلزی و غیرپلاستیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تعمیرکاران و تعویض‌کاران تایر خودرو</t>
+          <t>صافکار و نقاش خودرو | مونتاژکاران موتور و سایر ماشین‌آلات | لایه‌نشانان و سازندگان فایبرگلاس | مکانیک‌های ماشین‌آلات صنعتی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | دقت در کنترل | قدرت ایستا | قدرت بالاتنه | چابکی دستی | هماهنگی اندام‌ها | ثبات دست و بازو</t>
+          <t>بینایی نزدیک | دقت کنترل | قدرت ایستا | قدرت تنه | مهارت دستی | هماهنگی چند عضو | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارگران پرداخت‌کاری و سنگ‌زنی دستی | کارگران کمکی نصب، تعمیر و نگهداری | کارگران دستی حمل‌ونقل کالا و جابه‌جایی بار | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی</t>
+          <t>پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کارگران کمکی نصب، نگهداری و تعمیرات | کارگران جابه‌جایی دستی بار، کالا و مصالح | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت در کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کمک‌کارگران خطوط تولید | مونتاژکاران گروهی | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌کنندگان خطوط تولید | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تغذیه‌کنندگان و متصدیان تخلیه دستگاه‌های صنعتی | اپراتورهای ماشین‌ابزارهای CNC | مکانیک‌های ماشین‌آلات صنعتی</t>
+          <t>کمک‌کارگران خطوط تولید | مونتاژکاران گروهی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مکانیک‌های ماشین‌آلات صنعتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
